--- a/Thesis_TSSP_NEWNEW_M1_Results_10_Scenarios.xlsx
+++ b/Thesis_TSSP_NEWNEW_M1_Results_10_Scenarios.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4/5/2026 10:57</t>
+          <t>4/5/2026 10:49</t>
         </is>
       </c>
     </row>
@@ -500,32 +500,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>4/5/2026 09:13</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Transport Cart 1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>4/5/2026 15:35</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Transport Cart 3</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4/5/2026 15:35</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/5/2026 12:12</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
     </row>
@@ -547,17 +547,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 15:35</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -584,22 +584,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4/5/2026 15:35</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4/5/2026 09:58</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
     </row>
@@ -611,27 +611,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4/5/2026 14:39</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4/5/2026 15:33</t>
+          <t>4/5/2026 14:34</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -648,22 +648,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:20</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4/5/2026 15:33</t>
+          <t>4/5/2026 15:35</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -685,22 +685,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:49</t>
+          <t>4/5/2026 06:49</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:03</t>
+          <t>4/5/2026 07:02</t>
         </is>
       </c>
     </row>
@@ -722,27 +722,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4/5/2026 14:23</t>
+          <t>4/5/2026 15:35</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4/5/2026 11:51</t>
+          <t>4/5/2026 11:01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -759,22 +759,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4/5/2026 15:05</t>
+          <t>4/5/2026 15:15</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4/5/2026 08:44</t>
+          <t>4/5/2026 15:31</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4/5/2026 11:06</t>
+          <t>4/5/2026 10:58</t>
         </is>
       </c>
     </row>
@@ -796,27 +796,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4/5/2026 13:37</t>
+          <t>4/5/2026 15:22</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4/5/2026 10:45</t>
+          <t>4/5/2026 07:36</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4/5/2026 14:43</t>
+          <t>4/5/2026 12:15</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4/5/2026 12:38</t>
+          <t>4/5/2026 11:34</t>
         </is>
       </c>
     </row>
@@ -907,32 +907,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4/5/2026 13:19</t>
+          <t>4/5/2026 13:29</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4/5/2026 15:17</t>
+          <t>4/5/2026 14:53</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
     </row>
@@ -944,22 +944,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4/5/2026 07:07</t>
+          <t>4/5/2026 06:19</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4/5/2026 07:02</t>
+          <t>4/5/2026 10:06</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4/5/2026 14:14</t>
+          <t>4/5/2026 12:01</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1018,32 +1018,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:14</t>
+          <t>4/5/2026 11:31</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:14</t>
+          <t>4/5/2026 10:29</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
     </row>
@@ -1055,22 +1055,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4/5/2026 11:15</t>
+          <t>4/5/2026 11:10</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4/5/2026 11:28</t>
+          <t>4/5/2026 14:44</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1102,22 +1102,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4/5/2026 15:34</t>
+          <t>4/5/2026 10:58</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4/5/2026 10:20</t>
+          <t>4/5/2026 09:38</t>
         </is>
       </c>
     </row>
@@ -1139,22 +1139,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4/5/2026 15:29</t>
+          <t>4/5/2026 15:32</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4/5/2026 11:12</t>
+          <t>4/5/2026 11:21</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4/5/2026 11:58</t>
+          <t>4/5/2026 11:54</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4/5/2026 08:58</t>
+          <t>4/5/2026 10:32</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>437.30 min</t>
+          <t>433.90 min</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>34.58 min</t>
+          <t>31.28 min</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>85.30 min</t>
+          <t>84.60 min</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>98.00 min</t>
+          <t>92.00 min</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>24.30 min</t>
+          <t>10.40 min</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9.10/6.90/10.00 min</t>
+          <t>3.80/2.80/4.90 min</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>60.8180 sec</t>
+          <t>76.0020 sec</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.8728 %</t>
+          <t>1.2729 %</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>33.19 min | 84.00 min</t>
+          <t>30.10 min | 84.00 min</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32.19 min | 86.00 min</t>
+          <t>30.10 min | 86.00 min</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>37.57 min | 88.00 min</t>
+          <t>31.38 min | 88.00 min</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>35.90 min | 80.00 min</t>
+          <t>29.62 min | 80.00 min</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>37.95 min | 78.00 min</t>
+          <t>32.48 min | 78.00 min</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>34.67 min | 84.00 min</t>
+          <t>33.05 min | 84.00 min</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>34.48 min | 85.00 min</t>
+          <t>33.76 min | 85.00 min</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>34.38 min | 89.00 min</t>
+          <t>32.14 min | 89.00 min</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>32.38 min | 98.00 min</t>
+          <t>30.00 min | 92.00 min</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>33.05 min | 81.00 min</t>
+          <t>30.19 min | 80.00 min</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>13.91</v>
+        <v>18.69</v>
       </c>
     </row>
     <row r="41">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>11.59</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="42">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>11.59</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="43">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>11.59</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="44">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4.09</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="45">
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.72</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="46">
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="47">
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25.09</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="48">
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25.09</v>
+        <v>21.07</v>
       </c>
     </row>
     <row r="49">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>37.63</v>
+        <v>37.93</v>
       </c>
     </row>
   </sheetData>
@@ -2192,25 +2192,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4/5/2026 06:52</t>
+          <t>4/5/2026 06:48</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:01</t>
+          <t>4/5/2026 06:57</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:01</t>
+          <t>4/5/2026 06:57</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:03</t>
+          <t>4/5/2026 06:59</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -2218,22 +2218,22 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:03</t>
+          <t>4/5/2026 06:59</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:26</t>
+          <t>4/5/2026 07:22</t>
         </is>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2338,22 +2338,22 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4/5/2026 11:06</t>
+          <t>4/5/2026 10:57</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4/5/2026 11:18</t>
+          <t>4/5/2026 11:09</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2492,25 +2492,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:17</t>
+          <t>4/5/2026 11:15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:29</t>
+          <t>4/5/2026 11:27</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:32</t>
+          <t>4/5/2026 11:30</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:35</t>
+          <t>4/5/2026 11:33</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -2518,22 +2518,22 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:35</t>
+          <t>4/5/2026 11:33</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:55</t>
+          <t>4/5/2026 11:53</t>
         </is>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="N13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -2552,48 +2552,48 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 08:40</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:51</t>
+          <t>4/5/2026 08:46</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:52</t>
+          <t>4/5/2026 08:46</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:53</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:55</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="N14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2672,48 +2672,48 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>4/5/2026 07:08</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>4/5/2026 07:18</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>4/5/2026 07:28</t>
-        </is>
-      </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4/5/2026 07:35</t>
+          <t>4/5/2026 07:18</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4/5/2026 07:37</t>
+          <t>4/5/2026 07:20</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4/5/2026 07:47</t>
+          <t>4/5/2026 07:20</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4/5/2026 07:54</t>
+          <t>4/5/2026 07:27</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="N16" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2758,22 +2758,22 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2912,25 +2912,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4/5/2026 08:53</t>
+          <t>4/5/2026 08:45</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4/5/2026 09:07</t>
+          <t>4/5/2026 08:59</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4/5/2026 09:07</t>
+          <t>4/5/2026 08:59</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:00</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -2938,22 +2938,22 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4/5/2026 09:14</t>
+          <t>4/5/2026 09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>4/5/2026 09:40</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="N20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3298,22 +3298,22 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>4/5/2026 09:58</t>
+          <t>4/5/2026 09:57</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>4/5/2026 10:05</t>
+          <t>4/5/2026 10:04</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -3692,48 +3692,48 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4/5/2026 11:41</t>
+          <t>4/5/2026 11:48</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>4/5/2026 11:49</t>
+          <t>4/5/2026 11:56</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4/5/2026 11:49</t>
+          <t>4/5/2026 11:57</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4/5/2026 11:50</t>
+          <t>4/5/2026 11:58</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>4/5/2026 11:50</t>
+          <t>4/5/2026 11:58</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4/5/2026 11:56</t>
+          <t>4/5/2026 12:04</t>
         </is>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
@@ -3932,48 +3932,48 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:15</t>
+          <t>4/5/2026 07:08</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:26</t>
+          <t>4/5/2026 07:19</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:33</t>
+          <t>4/5/2026 07:19</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:35</t>
+          <t>4/5/2026 07:21</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:44</t>
+          <t>4/5/2026 07:21</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:51</t>
+          <t>4/5/2026 07:28</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="N37" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -4112,48 +4112,48 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>4/5/2026 09:33</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:33</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
           <t>4/5/2026 09:35</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v>2</v>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
         <is>
           <t>4/5/2026 09:35</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:37</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:40</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>4/5/2026 10:00</t>
+          <t>4/5/2026 09:55</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="N40" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -4172,25 +4172,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4/5/2026 10:02</t>
+          <t>4/5/2026 09:58</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>4/5/2026 10:24</t>
+          <t>4/5/2026 10:20</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>4/5/2026 10:24</t>
+          <t>4/5/2026 10:20</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4/5/2026 10:27</t>
+          <t>4/5/2026 10:23</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -4198,22 +4198,22 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>4/5/2026 10:28</t>
+          <t>4/5/2026 10:23</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>4/5/2026 10:55</t>
+          <t>4/5/2026 10:50</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="N41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -4232,48 +4232,48 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4/5/2026 11:35</t>
+          <t>4/5/2026 11:28</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4/5/2026 11:44</t>
+          <t>4/5/2026 11:37</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>4/5/2026 11:45</t>
+          <t>4/5/2026 11:37</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>4/5/2026 11:48</t>
+          <t>4/5/2026 11:40</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>4/5/2026 11:58</t>
+          <t>4/5/2026 11:40</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>4/5/2026 12:23</t>
+          <t>4/5/2026 12:05</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="N42" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -4292,25 +4292,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 08:57</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>12</v>
@@ -4352,48 +4352,48 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>4/5/2026 07:53</t>
+          <t>4/5/2026 07:46</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4/5/2026 08:04</t>
+          <t>4/5/2026 07:57</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>4/5/2026 08:10</t>
+          <t>4/5/2026 07:57</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>4/5/2026 08:12</t>
+          <t>4/5/2026 07:59</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>4/5/2026 08:22</t>
+          <t>4/5/2026 07:59</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>4/5/2026 08:49</t>
+          <t>4/5/2026 08:26</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="N44" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4472,25 +4472,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4/5/2026 12:48</t>
+          <t>4/5/2026 12:49</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4/5/2026 12:58</t>
+          <t>4/5/2026 12:59</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>4/5/2026 12:59</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>4/5/2026 13:01</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>21</v>
@@ -4532,48 +4532,48 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>4/5/2026 08:53</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>4/5/2026 08:55</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>4/5/2026 08:55</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>4/5/2026 08:56</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>4/5/2026 08:56</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t>4/5/2026 09:02</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:04</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
         <v>9</v>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:11</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:12</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>7</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:18</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:24</t>
-        </is>
-      </c>
-      <c r="L47" t="n">
-        <v>6</v>
-      </c>
-      <c r="M47" t="n">
-        <v>31</v>
-      </c>
       <c r="N47" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -4592,48 +4592,48 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>4/5/2026 09:26</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="N48" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -4712,25 +4712,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>4/5/2026 06:49</t>
+          <t>4/5/2026 06:48</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>4/5/2026 07:01</t>
+          <t>4/5/2026 07:00</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>4/5/2026 07:01</t>
+          <t>4/5/2026 07:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4/5/2026 07:03</t>
+          <t>4/5/2026 07:02</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>4/5/2026 07:03</t>
+          <t>4/5/2026 07:02</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>4/5/2026 07:26</t>
+          <t>4/5/2026 07:25</t>
         </is>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -4858,22 +4858,22 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>4/5/2026 11:05</t>
+          <t>4/5/2026 11:02</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>4/5/2026 11:17</t>
+          <t>4/5/2026 11:14</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="N52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -4892,48 +4892,48 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4/5/2026 07:35</t>
+          <t>4/5/2026 07:25</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>4/5/2026 07:41</t>
+          <t>4/5/2026 07:31</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>4/5/2026 07:48</t>
+          <t>4/5/2026 07:31</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4/5/2026 07:51</t>
+          <t>4/5/2026 07:34</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>4/5/2026 07:51</t>
+          <t>4/5/2026 07:34</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>4/5/2026 08:06</t>
+          <t>4/5/2026 07:49</t>
         </is>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="N53" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -4965,35 +4965,35 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>4/5/2026 08:13</t>
+          <t>4/5/2026 08:12</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4/5/2026 08:15</t>
+          <t>4/5/2026 08:14</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>4/5/2026 08:16</t>
+          <t>4/5/2026 08:14</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>4/5/2026 08:36</t>
+          <t>4/5/2026 08:34</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -5012,48 +5012,48 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>4/5/2026 11:16</t>
+          <t>4/5/2026 11:13</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>4/5/2026 11:27</t>
+          <t>4/5/2026 11:24</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>4/5/2026 11:28</t>
+          <t>4/5/2026 11:24</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>4/5/2026 11:30</t>
+          <t>4/5/2026 11:26</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>4/5/2026 11:35</t>
+          <t>4/5/2026 11:26</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>4/5/2026 11:55</t>
+          <t>4/5/2026 11:46</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="N55" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -5192,48 +5192,48 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>4/5/2026 07:18</t>
+          <t>4/5/2026 07:08</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:20</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>4/5/2026 07:37</t>
+          <t>4/5/2026 07:20</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4/5/2026 07:38</t>
+          <t>4/5/2026 07:21</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>4/5/2026 07:43</t>
+          <t>4/5/2026 07:21</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>4/5/2026 07:50</t>
+          <t>4/5/2026 07:28</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="N58" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -5265,35 +5265,35 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:18</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -5492,48 +5492,48 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>4/5/2026 10:08</t>
+          <t>4/5/2026 10:01</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>4/5/2026 10:19</t>
+          <t>4/5/2026 10:12</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>4/5/2026 10:23</t>
+          <t>4/5/2026 10:12</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>4/5/2026 10:25</t>
+          <t>4/5/2026 10:14</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>4/5/2026 10:29</t>
+          <t>4/5/2026 10:14</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>4/5/2026 10:53</t>
+          <t>4/5/2026 10:38</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="N63" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -5612,48 +5612,48 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>4/5/2026 07:52</t>
+          <t>4/5/2026 07:46</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>4/5/2026 08:01</t>
+          <t>4/5/2026 07:55</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>4/5/2026 08:08</t>
+          <t>4/5/2026 07:55</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>4/5/2026 08:10</t>
+          <t>4/5/2026 07:57</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>4/5/2026 08:19</t>
+          <t>4/5/2026 07:57</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>4/5/2026 08:46</t>
+          <t>4/5/2026 08:24</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="N65" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -5732,48 +5732,48 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>4/5/2026 06:09</t>
+          <t>4/5/2026 06:00</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>4/5/2026 06:10</t>
+          <t>4/5/2026 06:01</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>4/5/2026 06:15</t>
+          <t>4/5/2026 06:01</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>4/5/2026 06:17</t>
+          <t>4/5/2026 06:03</t>
         </is>
       </c>
       <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>4/5/2026 06:03</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>4/5/2026 06:05</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
         <v>5</v>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>4/5/2026 06:26</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>4/5/2026 06:28</t>
-        </is>
-      </c>
-      <c r="L67" t="n">
-        <v>9</v>
-      </c>
-      <c r="M67" t="n">
-        <v>28</v>
-      </c>
       <c r="N67" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -5792,48 +5792,48 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 08:53</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 08:57</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 08:57</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="N68" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -6032,48 +6032,48 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
+          <t>4/5/2026 09:29</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:29</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
           <t>4/5/2026 09:30</t>
         </is>
       </c>
-      <c r="F72" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:36</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:37</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>4/5/2026 09:47</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>4/5/2026 10:28</t>
+          <t>4/5/2026 10:14</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M72" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="N72" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -6285,35 +6285,35 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>4/5/2026 12:43</t>
+          <t>4/5/2026 12:40</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>4/5/2026 12:45</t>
+          <t>4/5/2026 12:42</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>4/5/2026 12:54</t>
+          <t>4/5/2026 12:42</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>4/5/2026 13:25</t>
+          <t>4/5/2026 13:13</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="N76" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -6645,35 +6645,35 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>4/5/2026 09:41</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>4/5/2026 09:43</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>4/5/2026 09:45</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>4/5/2026 10:05</t>
+          <t>4/5/2026 09:56</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="N82" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -6705,35 +6705,35 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 08:57</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 08:57</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>4/5/2026 09:39</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="N83" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -6752,48 +6752,48 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>4/5/2026 10:02</t>
+          <t>4/5/2026 10:01</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>4/5/2026 10:14</t>
+          <t>4/5/2026 10:13</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>4/5/2026 10:17</t>
+          <t>4/5/2026 10:13</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>4/5/2026 10:19</t>
+          <t>4/5/2026 10:15</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>4/5/2026 10:29</t>
+          <t>4/5/2026 10:15</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>4/5/2026 10:53</t>
+          <t>4/5/2026 10:39</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="N84" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -6992,48 +6992,48 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>4/5/2026 12:58</t>
+          <t>4/5/2026 12:48</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>4/5/2026 13:10</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>4/5/2026 13:17</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>4/5/2026 13:19</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>4/5/2026 13:23</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>4/5/2026 13:30</t>
+          <t>4/5/2026 13:09</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="N88" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -7052,48 +7052,48 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>4/5/2026 13:00</t>
+          <t>4/5/2026 12:50</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>4/5/2026 13:05</t>
+          <t>4/5/2026 12:55</t>
         </is>
       </c>
       <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>4/5/2026 12:57</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>4/5/2026 12:59</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>2</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>4/5/2026 13:09</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>4/5/2026 13:36</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
         <v>10</v>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>4/5/2026 13:05</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>4/5/2026 13:07</t>
-        </is>
-      </c>
-      <c r="I89" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>4/5/2026 13:15</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>4/5/2026 13:42</t>
-        </is>
-      </c>
-      <c r="L89" t="n">
-        <v>8</v>
-      </c>
       <c r="M89" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="N89" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90">
@@ -7185,35 +7185,35 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
+          <t>4/5/2026 07:28</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
           <t>4/5/2026 07:29</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>4/5/2026 07:30</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:29</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 07:45</t>
         </is>
       </c>
       <c r="L91" t="n">
         <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -7318,22 +7318,22 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>4/5/2026 09:40</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>4/5/2026 10:21</t>
+          <t>4/5/2026 10:15</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M93" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="N93" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
@@ -7412,48 +7412,48 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:25</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>4/5/2026 07:34</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>4/5/2026 07:41</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>4/5/2026 07:43</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>4/5/2026 07:53</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>4/5/2026 08:08</t>
+          <t>4/5/2026 07:47</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="N95" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -7532,48 +7532,48 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>4/5/2026 12:33</t>
+          <t>4/5/2026 12:23</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>4/5/2026 12:46</t>
+          <t>4/5/2026 12:36</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>4/5/2026 12:50</t>
+          <t>4/5/2026 12:36</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>4/5/2026 12:52</t>
+          <t>4/5/2026 12:38</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>4/5/2026 12:52</t>
+          <t>4/5/2026 12:38</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>4/5/2026 13:23</t>
+          <t>4/5/2026 13:09</t>
         </is>
       </c>
       <c r="L97" t="n">
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="N97" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -7592,48 +7592,48 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>4/5/2026 08:48</t>
+          <t>4/5/2026 08:40</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>4/5/2026 08:53</t>
+          <t>4/5/2026 08:45</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>4/5/2026 09:00</t>
+          <t>4/5/2026 08:45</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>4/5/2026 09:39</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="N98" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -7892,25 +7892,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>4/5/2026 09:26</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>4/5/2026 09:44</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>4/5/2026 09:44</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4/5/2026 09:47</t>
+          <t>4/5/2026 09:37</t>
         </is>
       </c>
       <c r="I103" t="n">
@@ -7918,22 +7918,22 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>4/5/2026 09:49</t>
+          <t>4/5/2026 09:37</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>4/5/2026 10:09</t>
+          <t>4/5/2026 09:57</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N103" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -7952,48 +7952,48 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>4/5/2026 08:55</t>
+          <t>4/5/2026 08:48</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:01</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 09:07</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>4/5/2026 09:45</t>
+          <t>4/5/2026 09:35</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N104" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="105">
@@ -8252,48 +8252,48 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>4/5/2026 06:01</t>
+          <t>4/5/2026 06:00</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
+          <t>4/5/2026 06:02</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>4/5/2026 06:02</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
           <t>4/5/2026 06:03</t>
         </is>
       </c>
-      <c r="F109" t="n">
-        <v>1</v>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>4/5/2026 06:07</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>4/5/2026 06:08</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>4/5/2026 06:17</t>
+          <t>4/5/2026 06:03</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>4/5/2026 06:19</t>
+          <t>4/5/2026 06:05</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="N109" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -8312,25 +8312,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>4/5/2026 11:53</t>
+          <t>4/5/2026 11:47</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4/5/2026 11:54</t>
+          <t>4/5/2026 11:48</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>4/5/2026 11:54</t>
+          <t>4/5/2026 11:48</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>4/5/2026 11:56</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
       <c r="I110" t="n">
@@ -8338,22 +8338,22 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>4/5/2026 11:56</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>4/5/2026 12:01</t>
+          <t>4/5/2026 11:55</t>
         </is>
       </c>
       <c r="L110" t="n">
         <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="N110" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -8372,48 +8372,48 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
+          <t>4/5/2026 09:08</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
           <t>4/5/2026 09:09</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:10</t>
-        </is>
-      </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
+          <t>4/5/2026 09:11</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:11</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t>4/5/2026 09:12</t>
         </is>
       </c>
-      <c r="I111" t="n">
-        <v>0</v>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:12</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:13</t>
-        </is>
-      </c>
       <c r="L111" t="n">
         <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -8458,22 +8458,22 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>4/5/2026 07:47</t>
+          <t>4/5/2026 07:46</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -8492,25 +8492,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>4/5/2026 06:51</t>
+          <t>4/5/2026 06:48</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>4/5/2026 07:01</t>
+          <t>4/5/2026 06:58</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>4/5/2026 07:01</t>
+          <t>4/5/2026 06:58</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>4/5/2026 07:03</t>
+          <t>4/5/2026 07:00</t>
         </is>
       </c>
       <c r="I113" t="n">
@@ -8518,22 +8518,22 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>4/5/2026 07:03</t>
+          <t>4/5/2026 07:00</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>4/5/2026 07:26</t>
+          <t>4/5/2026 07:23</t>
         </is>
       </c>
       <c r="L113" t="n">
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="N113" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -8625,35 +8625,35 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
+          <t>4/5/2026 08:37</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
           <t>4/5/2026 08:40</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>4/5/2026 08:43</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 08:40</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N115" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -8792,48 +8792,48 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>4/5/2026 12:29</t>
+          <t>4/5/2026 12:23</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>4/5/2026 12:41</t>
+          <t>4/5/2026 12:35</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>4/5/2026 12:47</t>
+          <t>4/5/2026 12:35</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>4/5/2026 12:49</t>
+          <t>4/5/2026 12:37</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>4/5/2026 12:58</t>
+          <t>4/5/2026 12:37</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>4/5/2026 13:29</t>
+          <t>4/5/2026 13:08</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="N118" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -9058,22 +9058,22 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -9152,48 +9152,48 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>4/5/2026 12:26</t>
+          <t>4/5/2026 12:36</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>4/5/2026 12:43</t>
+          <t>4/5/2026 12:53</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>4/5/2026 12:43</t>
+          <t>4/5/2026 12:56</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>4/5/2026 12:45</t>
+          <t>4/5/2026 12:58</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>4/5/2026 12:45</t>
+          <t>4/5/2026 13:08</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>4/5/2026 13:14</t>
+          <t>4/5/2026 13:37</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M124" t="n">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="125">
@@ -9272,48 +9272,48 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>4/5/2026 08:41</t>
+          <t>4/5/2026 08:42</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 08:57</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 08:58</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:00</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>4/5/2026 09:48</t>
+          <t>4/5/2026 09:43</t>
         </is>
       </c>
       <c r="L126" t="n">
         <v>10</v>
       </c>
       <c r="M126" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="N126" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="127">
@@ -9392,48 +9392,48 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>4/5/2026 07:50</t>
+          <t>4/5/2026 07:46</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>4/5/2026 08:00</t>
+          <t>4/5/2026 07:56</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>4/5/2026 08:07</t>
+          <t>4/5/2026 07:56</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>4/5/2026 08:09</t>
+          <t>4/5/2026 07:58</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>4/5/2026 08:09</t>
+          <t>4/5/2026 07:58</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>4/5/2026 08:36</t>
+          <t>4/5/2026 08:25</t>
         </is>
       </c>
       <c r="L128" t="n">
         <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="N128" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -9598,22 +9598,22 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>4/5/2026 11:54</t>
+          <t>4/5/2026 11:51</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>4/5/2026 11:59</t>
+          <t>4/5/2026 11:56</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N131" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -9645,35 +9645,35 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
+          <t>4/5/2026 09:11</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:11</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t>4/5/2026 09:12</t>
         </is>
       </c>
-      <c r="I132" t="n">
-        <v>1</v>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:12</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:13</t>
-        </is>
-      </c>
       <c r="L132" t="n">
         <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -9872,16 +9872,16 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>4/5/2026 12:51</t>
+          <t>4/5/2026 12:50</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>4/5/2026 12:56</t>
+          <t>4/5/2026 12:55</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -9992,25 +9992,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>4/5/2026 11:41</t>
+          <t>4/5/2026 11:43</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>4/5/2026 11:51</t>
+          <t>4/5/2026 11:53</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>4/5/2026 11:51</t>
+          <t>4/5/2026 11:53</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>4/5/2026 11:52</t>
+          <t>4/5/2026 11:54</t>
         </is>
       </c>
       <c r="I138" t="n">
@@ -10018,22 +10018,22 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>4/5/2026 11:52</t>
+          <t>4/5/2026 11:54</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>4/5/2026 11:58</t>
+          <t>4/5/2026 12:00</t>
         </is>
       </c>
       <c r="L138" t="n">
         <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139">
@@ -10052,48 +10052,48 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>4/5/2026 12:31</t>
+          <t>4/5/2026 12:23</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>4/5/2026 12:48</t>
+          <t>4/5/2026 12:40</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>4/5/2026 12:55</t>
+          <t>4/5/2026 12:40</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>4/5/2026 12:56</t>
+          <t>4/5/2026 12:41</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>4/5/2026 13:06</t>
+          <t>4/5/2026 12:41</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>4/5/2026 13:37</t>
+          <t>4/5/2026 13:12</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="N139" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -10305,35 +10305,35 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
+          <t>4/5/2026 09:18</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
           <t>4/5/2026 09:19</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:20</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N143" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -10412,48 +10412,48 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>4/5/2026 12:26</t>
+          <t>4/5/2026 12:36</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>4/5/2026 12:43</t>
+          <t>4/5/2026 12:53</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>4/5/2026 12:43</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>4/5/2026 12:45</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>4/5/2026 12:47</t>
+          <t>4/5/2026 13:12</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>4/5/2026 13:16</t>
+          <t>4/5/2026 13:41</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M145" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N145" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="146">
@@ -10678,22 +10678,22 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>4/5/2026 07:59</t>
+          <t>4/5/2026 07:58</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>4/5/2026 08:26</t>
+          <t>4/5/2026 08:25</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -10832,48 +10832,48 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
+          <t>4/5/2026 08:53</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
           <t>4/5/2026 08:56</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>4/5/2026 08:59</t>
-        </is>
-      </c>
       <c r="F152" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
+          <t>4/5/2026 08:58</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:02</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t>4/5/2026 09:08</t>
         </is>
       </c>
-      <c r="I152" t="n">
-        <v>7</v>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:08</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:14</t>
-        </is>
-      </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M152" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="N152" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="153">
@@ -11158,22 +11158,22 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>4/5/2026 12:47</t>
+          <t>4/5/2026 12:51</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>4/5/2026 13:16</t>
+          <t>4/5/2026 13:20</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M157" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="158">
@@ -11192,48 +11192,48 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>4/5/2026 07:35</t>
+          <t>4/5/2026 07:25</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>4/5/2026 07:39</t>
+          <t>4/5/2026 07:29</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>4/5/2026 07:44</t>
+          <t>4/5/2026 07:29</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
+          <t>4/5/2026 07:31</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>4/5/2026 07:31</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t>4/5/2026 07:46</t>
         </is>
       </c>
-      <c r="I158" t="n">
-        <v>5</v>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>4/5/2026 07:56</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>4/5/2026 08:11</t>
-        </is>
-      </c>
       <c r="L158" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="N158" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -11312,25 +11312,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>4/5/2026 08:27</t>
+          <t>4/5/2026 08:24</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>4/5/2026 08:37</t>
+          <t>4/5/2026 08:34</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>4/5/2026 08:37</t>
+          <t>4/5/2026 08:34</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>4/5/2026 08:38</t>
+          <t>4/5/2026 08:35</t>
         </is>
       </c>
       <c r="I160" t="n">
@@ -11338,22 +11338,22 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>4/5/2026 08:38</t>
+          <t>4/5/2026 08:35</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="L160" t="n">
         <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="N160" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -11518,22 +11518,22 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>4/5/2026 07:33</t>
+          <t>4/5/2026 07:23</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>4/5/2026 07:40</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="N163" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -11578,22 +11578,22 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>4/5/2026 09:32</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -11698,22 +11698,22 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>4/5/2026 12:51</t>
+          <t>4/5/2026 12:45</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>4/5/2026 13:20</t>
+          <t>4/5/2026 13:14</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="N166" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -11732,29 +11732,29 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>4/5/2026 11:58</t>
+          <t>4/5/2026 11:59</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>4/5/2026 12:07</t>
+          <t>4/5/2026 12:08</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>4/5/2026 12:09</t>
+          <t>4/5/2026 12:15</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>4/5/2026 12:13</t>
+          <t>4/5/2026 12:19</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M167" t="n">
         <v>53</v>
@@ -11818,22 +11818,22 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>4/5/2026 11:55</t>
+          <t>4/5/2026 11:53</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>4/5/2026 12:25</t>
+          <t>4/5/2026 12:23</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -11878,22 +11878,22 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M169" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N169" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170">
@@ -11938,22 +11938,22 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>4/5/2026 11:49</t>
+          <t>4/5/2026 11:56</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>4/5/2026 12:12</t>
+          <t>4/5/2026 12:19</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M170" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="171">
@@ -11972,25 +11972,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>4/5/2026 09:45</t>
+          <t>4/5/2026 09:39</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>4/5/2026 09:45</t>
+          <t>4/5/2026 09:39</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>4/5/2026 09:47</t>
+          <t>4/5/2026 09:41</t>
         </is>
       </c>
       <c r="I171" t="n">
@@ -11998,22 +11998,22 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>4/5/2026 09:47</t>
+          <t>4/5/2026 09:41</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>4/5/2026 10:51</t>
+          <t>4/5/2026 10:45</t>
         </is>
       </c>
       <c r="L171" t="n">
         <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="N171" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -12058,22 +12058,22 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>4/5/2026 13:11</t>
+          <t>4/5/2026 13:03</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>4/5/2026 13:18</t>
+          <t>4/5/2026 13:10</t>
         </is>
       </c>
       <c r="L172" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N172" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -12465,35 +12465,35 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>4/5/2026 07:36</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>4/5/2026 07:38</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="I179" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>4/5/2026 07:48</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>4/5/2026 08:03</t>
+          <t>4/5/2026 07:47</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="N179" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -12585,35 +12585,35 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>4/5/2026 12:38</t>
+          <t>4/5/2026 12:35</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>4/5/2026 12:40</t>
+          <t>4/5/2026 12:37</t>
         </is>
       </c>
       <c r="I181" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>4/5/2026 12:40</t>
+          <t>4/5/2026 12:37</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>4/5/2026 13:11</t>
+          <t>4/5/2026 13:08</t>
         </is>
       </c>
       <c r="L181" t="n">
         <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="N181" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -12632,48 +12632,48 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
+          <t>4/5/2026 08:40</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
           <t>4/5/2026 08:46</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>4/5/2026 08:52</t>
-        </is>
-      </c>
       <c r="F182" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>4/5/2026 08:58</t>
+          <t>4/5/2026 08:46</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>4/5/2026 08:59</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="I182" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="N182" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -12838,22 +12838,22 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>4/5/2026 09:32</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N185" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -13198,22 +13198,22 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>4/5/2026 10:57</t>
+          <t>4/5/2026 10:56</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>4/5/2026 11:31</t>
+          <t>4/5/2026 11:30</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M191" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -13245,35 +13245,35 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>4/5/2026 12:07</t>
+          <t>4/5/2026 12:06</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>4/5/2026 12:09</t>
+          <t>4/5/2026 12:08</t>
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>4/5/2026 12:09</t>
+          <t>4/5/2026 12:08</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>4/5/2026 12:55</t>
+          <t>4/5/2026 12:54</t>
         </is>
       </c>
       <c r="L192" t="n">
         <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -13292,48 +13292,48 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>4/5/2026 06:02</t>
+          <t>4/5/2026 06:00</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
+          <t>4/5/2026 06:01</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>4/5/2026 06:01</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
           <t>4/5/2026 06:03</t>
         </is>
       </c>
-      <c r="F193" t="n">
-        <v>2</v>
-      </c>
-      <c r="G193" t="inlineStr">
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" t="inlineStr">
         <is>
           <t>4/5/2026 06:03</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
+      <c r="K193" t="inlineStr">
         <is>
           <t>4/5/2026 06:05</t>
         </is>
       </c>
-      <c r="I193" t="n">
-        <v>0</v>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>4/5/2026 06:06</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>4/5/2026 06:08</t>
-        </is>
-      </c>
       <c r="L193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N193" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -13352,48 +13352,48 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>4/5/2026 12:57</t>
+          <t>4/5/2026 12:50</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>4/5/2026 13:00</t>
+          <t>4/5/2026 12:53</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>4/5/2026 13:07</t>
+          <t>4/5/2026 12:53</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>4/5/2026 13:09</t>
+          <t>4/5/2026 12:55</t>
         </is>
       </c>
       <c r="I194" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>4/5/2026 13:19</t>
+          <t>4/5/2026 12:55</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>4/5/2026 13:46</t>
+          <t>4/5/2026 13:22</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M194" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="N194" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -13485,35 +13485,35 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:28</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>4/5/2026 07:47</t>
+          <t>4/5/2026 07:46</t>
         </is>
       </c>
       <c r="L196" t="n">
         <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -13618,22 +13618,22 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:35</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>4/5/2026 10:18</t>
+          <t>4/5/2026 10:16</t>
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N198" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -13772,25 +13772,25 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>4/5/2026 11:41</t>
+          <t>4/5/2026 11:45</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>4/5/2026 11:49</t>
+          <t>4/5/2026 11:53</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>4/5/2026 11:49</t>
+          <t>4/5/2026 11:53</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>4/5/2026 11:51</t>
+          <t>4/5/2026 11:55</t>
         </is>
       </c>
       <c r="I201" t="n">
@@ -13798,22 +13798,22 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>4/5/2026 11:51</t>
+          <t>4/5/2026 11:55</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>4/5/2026 11:57</t>
+          <t>4/5/2026 12:01</t>
         </is>
       </c>
       <c r="L201" t="n">
         <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="202">
@@ -13832,48 +13832,48 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
+          <t>4/5/2026 11:13</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
           <t>4/5/2026 11:23</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:33</t>
-        </is>
-      </c>
       <c r="F202" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>4/5/2026 11:40</t>
+          <t>4/5/2026 11:23</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>4/5/2026 11:42</t>
+          <t>4/5/2026 11:25</t>
         </is>
       </c>
       <c r="I202" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>4/5/2026 11:42</t>
+          <t>4/5/2026 11:30</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>4/5/2026 12:02</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
       <c r="L202" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M202" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="N202" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="203">
@@ -13905,35 +13905,35 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>4/5/2026 11:22</t>
+          <t>4/5/2026 11:16</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>4/5/2026 11:24</t>
+          <t>4/5/2026 11:18</t>
         </is>
       </c>
       <c r="I203" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>4/5/2026 11:34</t>
+          <t>4/5/2026 11:18</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>4/5/2026 12:11</t>
+          <t>4/5/2026 11:55</t>
         </is>
       </c>
       <c r="L203" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="N203" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -14192,25 +14192,25 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>4/5/2026 09:40</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>4/5/2026 09:40</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>4/5/2026 09:42</t>
+          <t>4/5/2026 09:38</t>
         </is>
       </c>
       <c r="I208" t="n">
@@ -14218,22 +14218,22 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>4/5/2026 09:42</t>
+          <t>4/5/2026 09:38</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>4/5/2026 10:02</t>
+          <t>4/5/2026 09:58</t>
         </is>
       </c>
       <c r="L208" t="n">
         <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N208" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209">
